--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-4B-Instruct-2507/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-4B-Instruct-2507/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>320</v>
+        <v>285</v>
       </c>
       <c r="D2">
-        <v>47</v>
+        <v>132</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>112</v>
+        <v>275</v>
       </c>
       <c r="D3">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="E3">
-        <v>108</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-4B-Instruct-2507/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-4B-Instruct-2507/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D2">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D3">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H3">
         <v>426</v>
